--- a/table/resources/sample/betsample/WinPosWeight.xlsx
+++ b/table/resources/sample/betsample/WinPosWeight.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="WinPosWeight" sheetId="20" r:id="rId1"/>
@@ -4411,10 +4411,10 @@
         <v>13</v>
       </c>
       <c r="F43" s="2">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G43" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>79</v>
@@ -5098,10 +5098,10 @@
         <v>27</v>
       </c>
       <c r="F57" s="2">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="G57" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>79</v>
@@ -6349,7 +6349,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="2">
-        <v>1</v>
+        <v>104</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
@@ -6396,7 +6396,7 @@
         <v>2</v>
       </c>
       <c r="F84" s="2">
-        <v>700</v>
+        <v>205</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
@@ -6443,7 +6443,7 @@
         <v>3</v>
       </c>
       <c r="F85" s="2">
-        <v>1300</v>
+        <v>205</v>
       </c>
       <c r="G85" s="2">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>4</v>
       </c>
       <c r="F86" s="2">
-        <v>820</v>
+        <v>52</v>
       </c>
       <c r="G86" s="2">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>5</v>
       </c>
       <c r="F87" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
@@ -6584,7 +6584,7 @@
         <v>6</v>
       </c>
       <c r="F88" s="2">
-        <v>380</v>
+        <v>205</v>
       </c>
       <c r="G88" s="2">
         <v>0</v>
@@ -6631,7 +6631,7 @@
         <v>7</v>
       </c>
       <c r="F89" s="2">
-        <v>750</v>
+        <v>206</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>8</v>
       </c>
       <c r="F90" s="2">
-        <v>450</v>
+        <v>205</v>
       </c>
       <c r="G90" s="2">
         <v>0</v>
@@ -6725,7 +6725,7 @@
         <v>9</v>
       </c>
       <c r="F91" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="G91" s="2">
         <v>0</v>
@@ -6772,7 +6772,7 @@
         <v>10</v>
       </c>
       <c r="F92" s="2">
-        <v>1140</v>
+        <v>70</v>
       </c>
       <c r="G92" s="2">
         <v>0</v>
@@ -6819,7 +6819,7 @@
         <v>11</v>
       </c>
       <c r="F93" s="2">
-        <v>2300</v>
+        <v>205</v>
       </c>
       <c r="G93" s="2">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         <v>12</v>
       </c>
       <c r="F94" s="2">
-        <v>1300</v>
+        <v>205</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
@@ -6913,7 +6913,7 @@
         <v>13</v>
       </c>
       <c r="F95" s="2">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="G95" s="2">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         <v>14</v>
       </c>
       <c r="F96" s="2">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
@@ -7007,7 +7007,7 @@
         <v>15</v>
       </c>
       <c r="F97" s="2">
-        <v>350</v>
+        <v>205</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
@@ -7054,7 +7054,7 @@
         <v>16</v>
       </c>
       <c r="F98" s="2">
-        <v>230</v>
+        <v>52</v>
       </c>
       <c r="G98" s="2">
         <v>0</v>
@@ -7101,7 +7101,7 @@
         <v>17</v>
       </c>
       <c r="F99" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
@@ -7148,7 +7148,7 @@
         <v>18</v>
       </c>
       <c r="F100" s="2">
-        <v>900</v>
+        <v>205</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>19</v>
       </c>
       <c r="F101" s="2">
-        <v>450</v>
+        <v>206</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>20</v>
       </c>
       <c r="F102" s="2">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="G102" s="2">
         <v>0</v>
@@ -7289,7 +7289,7 @@
         <v>21</v>
       </c>
       <c r="F103" s="2">
-        <v>1140</v>
+        <v>205</v>
       </c>
       <c r="G103" s="2">
         <v>0</v>
@@ -7336,7 +7336,7 @@
         <v>22</v>
       </c>
       <c r="F104" s="2">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
@@ -7383,7 +7383,7 @@
         <v>23</v>
       </c>
       <c r="F105" s="2">
-        <v>1300</v>
+        <v>205</v>
       </c>
       <c r="G105" s="2">
         <v>0</v>
@@ -7430,7 +7430,7 @@
         <v>24</v>
       </c>
       <c r="F106" s="2">
-        <v>2300</v>
+        <v>205</v>
       </c>
       <c r="G106" s="2">
         <v>0</v>

--- a/table/resources/sample/betsample/WinPosWeight.xlsx
+++ b/table/resources/sample/betsample/WinPosWeight.xlsx
@@ -15125,7 +15125,7 @@
         <v>230</v>
       </c>
       <c r="E268" s="2">
-        <v>1</v>
+        <v>1112</v>
       </c>
       <c r="F268" s="2">
         <v>4</v>
@@ -15169,7 +15169,7 @@
         <v>232</v>
       </c>
       <c r="E269" s="2">
-        <v>2</v>
+        <v>2221</v>
       </c>
       <c r="F269" s="2">
         <v>4</v>
@@ -15213,7 +15213,7 @@
         <v>234</v>
       </c>
       <c r="E270" s="2">
-        <v>3</v>
+        <v>2222</v>
       </c>
       <c r="F270" s="2">
         <v>1</v>
@@ -15257,7 +15257,7 @@
         <v>236</v>
       </c>
       <c r="E271" s="2">
-        <v>4</v>
+        <v>1122</v>
       </c>
       <c r="F271" s="2">
         <v>6</v>
@@ -15301,7 +15301,7 @@
         <v>239</v>
       </c>
       <c r="E272" s="2">
-        <v>5</v>
+        <v>1111</v>
       </c>
       <c r="F272" s="2">
         <v>1</v>
@@ -15345,7 +15345,7 @@
         <v>230</v>
       </c>
       <c r="E273" s="2">
-        <v>1</v>
+        <v>1112</v>
       </c>
       <c r="F273" s="2">
         <v>4</v>
@@ -15389,7 +15389,7 @@
         <v>232</v>
       </c>
       <c r="E274" s="2">
-        <v>2</v>
+        <v>2221</v>
       </c>
       <c r="F274" s="2">
         <v>4</v>
@@ -15433,7 +15433,7 @@
         <v>234</v>
       </c>
       <c r="E275" s="2">
-        <v>3</v>
+        <v>2222</v>
       </c>
       <c r="F275" s="2">
         <v>1</v>
@@ -15477,7 +15477,7 @@
         <v>239</v>
       </c>
       <c r="E276" s="2">
-        <v>5</v>
+        <v>1122</v>
       </c>
       <c r="F276" s="2">
         <v>1</v>

--- a/table/resources/sample/betsample/WinPosWeight.xlsx
+++ b/table/resources/sample/betsample/WinPosWeight.xlsx
@@ -15454,7 +15454,7 @@
         <v>1</v>
       </c>
       <c r="M275" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N275" s="14" t="s">
         <v>238</v>
@@ -15477,7 +15477,7 @@
         <v>239</v>
       </c>
       <c r="E276" s="2">
-        <v>1122</v>
+        <v>1111</v>
       </c>
       <c r="F276" s="2">
         <v>1</v>
@@ -15498,7 +15498,7 @@
         <v>1</v>
       </c>
       <c r="M276" s="12" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="N276" s="14" t="s">
         <v>238</v>
